--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -91,28 +91,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
   </si>
   <si>
     <t>JESUS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -620,16 +629,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>81.08</v>
+        <v>83.78</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -698,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>33</v>
@@ -707,7 +716,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H9">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -760,16 +769,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -783,16 +795,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>78.05</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -806,16 +821,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H4">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -829,16 +847,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H5">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -852,16 +873,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>81.08</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -875,16 +899,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -898,16 +925,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H8">
+        <v>8.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -921,16 +951,19 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>34</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>97.14</v>
+      </c>
+      <c r="H9">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -986,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1012,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>70.73</v>
+        <v>78.05</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1038,16 +1071,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>93.75</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1116,16 +1149,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1142,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>86.11</v>
+        <v>94.44</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1168,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9">
-        <v>94.29000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H9">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1187,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1219,22 +1252,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920090</v>
+        <v>24330051920129</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1242,39 +1275,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920132</v>
+        <v>24330051920373</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920053</v>
+        <v>24330051920038</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1283,6 +1316,29 @@
         <v>14</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -91,37 +91,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DIAZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>MAZABA</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
+    <t>JESUS</t>
   </si>
   <si>
     <t>MANUEL ABDUL</t>
   </si>
   <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
+    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,16 +1243,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920129</v>
+        <v>24330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1281,10 +1272,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1298,16 +1289,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920038</v>
+        <v>24330051920052</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1317,29 +1308,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -100,12 +103,27 @@
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>ANGEL ALBERTO</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
@@ -113,6 +131,12 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1243,22 +1267,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920132</v>
+        <v>24330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1266,22 +1290,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920373</v>
+        <v>24330051920132</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1289,16 +1313,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920052</v>
+        <v>24330051920373</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1307,6 +1331,75 @@
         <v>14</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920052</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920081</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -91,12 +91,36 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MAZABA</t>
   </si>
   <si>
@@ -112,6 +136,27 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE URIARTE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>QUINTERO</t>
   </si>
   <si>
@@ -119,6 +164,33 @@
   </si>
   <si>
     <t>BAEZ</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ELIAN RAMON</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ANDY ARELY</t>
   </si>
   <si>
     <t>ANGEL ALBERTO</t>
@@ -1235,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1267,139 +1339,346 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920340</v>
+        <v>24330051920038</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920132</v>
+        <v>23330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920373</v>
+        <v>24330051920338</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920052</v>
+        <v>24330051920332</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920081</v>
+        <v>24330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920113</v>
+        <v>24330051920335</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920060</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920028</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920340</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920132</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920373</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920052</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G7">
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920113</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -91,7 +91,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MOTA</t>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -100,115 +100,19 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>VILLARREAL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CHICUELLAR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE URIARTE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
+    <t>YERIEL</t>
   </si>
   <si>
     <t>IVONNE ERIMAR</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ELIAN RAMON</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ANDY ARELY</t>
-  </si>
-  <si>
-    <t>ANGEL ALBERTO</t>
-  </si>
-  <si>
     <t>JESUS</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -1106,13 +1010,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H2">
         <v>8.5</v>
@@ -1132,16 +1036,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>78.05</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1158,16 +1062,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1193,7 +1097,7 @@
         <v>97.22</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1210,16 +1114,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>81.08</v>
+        <v>94.59</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1236,16 +1140,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>87.88</v>
+        <v>96.97</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1262,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1307,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1339,22 +1243,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920038</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1368,10 +1272,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1380,305 +1284,29 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920338</v>
+        <v>24330051920132</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920332</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920065</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920335</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920129</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920060</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920028</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920340</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920132</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920373</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920052</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920113</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -94,25 +94,34 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>YERIEL</t>
   </si>
   <si>
+    <t>ULISES EZEQUIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,7 +1261,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1266,22 +1275,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920071</v>
+        <v>24330051920169</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1295,10 +1304,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1308,6 +1317,29 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920071</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -94,31 +94,49 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>VALDIVIA</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>YERIEL</t>
   </si>
   <si>
+    <t>IKER YHAIR</t>
+  </si>
+  <si>
     <t>ULISES EZEQUIEL</t>
   </si>
   <si>
     <t>JESUS</t>
+  </si>
+  <si>
+    <t>VANESSA GUADALUPE</t>
   </si>
   <si>
     <t>IVONNE ERIMAR</t>
@@ -1220,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,10 +1276,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1275,22 +1293,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920169</v>
+        <v>24330051920341</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1298,16 +1316,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920132</v>
+        <v>24330051920169</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1321,24 +1339,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920071</v>
+        <v>24330051920132</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920215</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920071</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>17</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
